--- a/artfynd/A 37669-2025 artfynd.xlsx
+++ b/artfynd/A 37669-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>127641630</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37669-2025 artfynd.xlsx
+++ b/artfynd/A 37669-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127641228</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127641630</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>127639064</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>127641576</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>127637947</v>
       </c>
       <c r="B7" t="n">
-        <v>95779</v>
+        <v>95781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127637958</v>
       </c>
       <c r="B8" t="n">
-        <v>95573</v>
+        <v>95575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37669-2025 artfynd.xlsx
+++ b/artfynd/A 37669-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127641228</v>
       </c>
       <c r="B3" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127641630</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>127639064</v>
       </c>
       <c r="B5" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>127641576</v>
       </c>
       <c r="B6" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>127637947</v>
       </c>
       <c r="B7" t="n">
-        <v>95781</v>
+        <v>95787</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127637958</v>
       </c>
       <c r="B8" t="n">
-        <v>95575</v>
+        <v>95581</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37669-2025 artfynd.xlsx
+++ b/artfynd/A 37669-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127641228</v>
       </c>
       <c r="B3" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127641630</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>127639064</v>
       </c>
       <c r="B5" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>127641576</v>
       </c>
       <c r="B6" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>127637947</v>
       </c>
       <c r="B7" t="n">
-        <v>95787</v>
+        <v>95790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127637958</v>
       </c>
       <c r="B8" t="n">
-        <v>95581</v>
+        <v>95584</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37669-2025 artfynd.xlsx
+++ b/artfynd/A 37669-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127641228</v>
       </c>
       <c r="B3" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127641630</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>127639064</v>
       </c>
       <c r="B5" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>127641576</v>
       </c>
       <c r="B6" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>127637947</v>
       </c>
       <c r="B7" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127637958</v>
       </c>
       <c r="B8" t="n">
-        <v>95584</v>
+        <v>95592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37669-2025 artfynd.xlsx
+++ b/artfynd/A 37669-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127641228</v>
       </c>
       <c r="B3" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127641630</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>127639064</v>
       </c>
       <c r="B5" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>127641576</v>
       </c>
       <c r="B6" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>127637947</v>
       </c>
       <c r="B7" t="n">
-        <v>95798</v>
+        <v>95799</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127637958</v>
       </c>
       <c r="B8" t="n">
-        <v>95592</v>
+        <v>95593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37669-2025 artfynd.xlsx
+++ b/artfynd/A 37669-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127641228</v>
       </c>
       <c r="B3" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127641630</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>127639064</v>
       </c>
       <c r="B5" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>127641576</v>
       </c>
       <c r="B6" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>127637947</v>
       </c>
       <c r="B7" t="n">
-        <v>95799</v>
+        <v>95800</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127637958</v>
       </c>
       <c r="B8" t="n">
-        <v>95593</v>
+        <v>95594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37669-2025 artfynd.xlsx
+++ b/artfynd/A 37669-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127641228</v>
       </c>
       <c r="B3" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127641630</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>127639064</v>
       </c>
       <c r="B5" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>127641576</v>
       </c>
       <c r="B6" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>127637947</v>
       </c>
       <c r="B7" t="n">
-        <v>95800</v>
+        <v>95801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127637958</v>
       </c>
       <c r="B8" t="n">
-        <v>95594</v>
+        <v>95595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
